--- a/Datos Experimentales/Data 24022.xlsx
+++ b/Datos Experimentales/Data 24022.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B979E88-ABC9-412B-B7A1-48509CD54DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1023,11 +1034,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1056,14 +1064,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1388,10 +1405,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B114"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1399,7 +1417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1407,7 +1425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1415,7 +1433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1423,7 +1441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1431,7 +1449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1439,7 +1457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1447,7 +1465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1455,7 +1473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1463,7 +1481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1471,7 +1489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1479,7 +1497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1487,7 +1505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1495,7 +1513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1503,7 +1521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1511,7 +1529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1519,7 +1537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1527,7 +1545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1535,7 +1553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1543,7 +1561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1551,7 +1569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1559,7 +1577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1567,7 +1585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1575,7 +1593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1583,7 +1601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1599,7 +1617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1607,7 +1625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1615,7 +1633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1623,7 +1641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1631,7 +1649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1639,7 +1657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1647,7 +1665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1655,7 +1673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1663,7 +1681,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1671,7 +1689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1679,7 +1697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1687,7 +1705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1695,7 +1713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1703,7 +1721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1711,7 +1729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1719,7 +1737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1727,7 +1745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1735,7 +1753,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1743,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1751,7 +1769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1759,7 +1777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1767,7 +1785,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1775,7 +1793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1783,7 +1801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1791,7 +1809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1799,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1807,7 +1825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1815,7 +1833,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1823,7 +1841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1831,7 +1849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1839,7 +1857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1847,7 +1865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1855,7 +1873,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1863,7 +1881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1871,7 +1889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1879,7 +1897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1887,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1895,7 +1913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1903,7 +1921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1911,7 +1929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1919,7 +1937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1927,7 +1945,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1935,7 +1953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1943,7 +1961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1951,7 +1969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -1959,7 +1977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -1967,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -1975,7 +1993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -1983,7 +2001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -1991,7 +2009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -1999,7 +2017,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -2007,7 +2025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -2015,7 +2033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>89</v>
       </c>
@@ -2023,7 +2041,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -2031,7 +2049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -2039,7 +2057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -2047,7 +2065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2055,7 +2073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2063,7 +2081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2071,7 +2089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2079,7 +2097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2087,7 +2105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2095,7 +2113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2103,7 +2121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2111,7 +2129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2119,7 +2137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2127,7 +2145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2135,7 +2153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2143,7 +2161,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -2151,7 +2169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -2159,7 +2177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -2167,7 +2185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2175,7 +2193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2183,7 +2201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2191,7 +2209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2199,7 +2217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2207,7 +2225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2215,7 +2233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2223,7 +2241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2231,7 +2249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2239,7 +2257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2247,7 +2265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2255,7 +2273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2263,7 +2281,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>123</v>
       </c>
@@ -2271,7 +2289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>124</v>
       </c>
@@ -2279,7 +2297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -2287,7 +2305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2295,7 +2313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2304,27 +2322,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B114"/>
+    <ignoredError sqref="A1:B114" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -2345,17 +2367,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>282</v>
       </c>
@@ -2366,458 +2390,458 @@
         <v>284</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>285</v>
       </c>
       <c r="B2">
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="C2">
         <v>17.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>286</v>
       </c>
       <c r="B3">
-        <v>0.475</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="C3">
         <v>17</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>287</v>
       </c>
       <c r="B4">
-        <v>0.725</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="C4">
         <v>17</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>288</v>
       </c>
       <c r="B5">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="C5">
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>289</v>
       </c>
       <c r="B6">
-        <v>1.225</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="C6">
         <v>16</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>290</v>
       </c>
       <c r="B7">
-        <v>1.475</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="C7">
         <v>17</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>291</v>
       </c>
       <c r="B8">
-        <v>1.725</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="C8">
         <v>16.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>292</v>
       </c>
       <c r="B9">
-        <v>1.975</v>
+        <v>1.9750000000000001</v>
       </c>
       <c r="C9">
         <v>16</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>293</v>
       </c>
       <c r="B10">
-        <v>2.225</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="C10">
         <v>16.5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>294</v>
       </c>
       <c r="B11">
-        <v>2.475</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="C11">
         <v>16.5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>295</v>
       </c>
       <c r="B12">
-        <v>2.725</v>
+        <v>2.7250000000000001</v>
       </c>
       <c r="C12">
         <v>16.5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>296</v>
       </c>
       <c r="B13">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="C13">
         <v>17</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>297</v>
       </c>
       <c r="B14">
-        <v>3.225</v>
+        <v>3.2250000000000001</v>
       </c>
       <c r="C14">
         <v>16.5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>298</v>
       </c>
       <c r="B15">
-        <v>3.475</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="C15">
         <v>16.5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>299</v>
       </c>
       <c r="B16">
-        <v>3.725</v>
+        <v>3.7250000000000001</v>
       </c>
       <c r="C16">
         <v>17</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>300</v>
       </c>
       <c r="B17">
-        <v>3.975</v>
+        <v>3.9750000000000001</v>
       </c>
       <c r="C17">
         <v>16.5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>301</v>
       </c>
       <c r="B18">
-        <v>4.225</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="C18">
-        <v>16.6</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>302</v>
       </c>
       <c r="B19">
-        <v>4.475</v>
+        <v>4.4749999999999996</v>
       </c>
       <c r="C19">
         <v>16.5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>303</v>
       </c>
       <c r="B20">
-        <v>4.725</v>
+        <v>4.7249999999999996</v>
       </c>
       <c r="C20">
         <v>16</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>304</v>
       </c>
       <c r="B21">
-        <v>4.975</v>
+        <v>4.9749999999999996</v>
       </c>
       <c r="C21">
         <v>16.5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>305</v>
       </c>
       <c r="B22">
-        <v>5.225</v>
+        <v>5.2249999999999996</v>
       </c>
       <c r="C22">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>306</v>
       </c>
       <c r="B23">
-        <v>5.475</v>
+        <v>5.4749999999999996</v>
       </c>
       <c r="C23">
         <v>16.2</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>307</v>
       </c>
       <c r="B24">
-        <v>5.725</v>
+        <v>5.7249999999999996</v>
       </c>
       <c r="C24">
         <v>16.5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>308</v>
       </c>
       <c r="B25">
-        <v>5.975</v>
+        <v>5.9749999999999996</v>
       </c>
       <c r="C25">
         <v>16.5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>309</v>
       </c>
       <c r="B26">
-        <v>6.225</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="C26">
         <v>16.7</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>310</v>
       </c>
       <c r="B27">
-        <v>6.475</v>
+        <v>6.4749999999999996</v>
       </c>
       <c r="C27">
         <v>16.5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>311</v>
       </c>
       <c r="B28">
-        <v>6.725</v>
+        <v>6.7249999999999996</v>
       </c>
       <c r="C28">
         <v>16.5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>312</v>
       </c>
       <c r="B29">
-        <v>6.975</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="C29">
         <v>16.5</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>313</v>
       </c>
       <c r="B30">
-        <v>7.225</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="C30">
-        <v>16.6</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>314</v>
       </c>
       <c r="B31">
-        <v>7.475</v>
+        <v>7.4749999999999996</v>
       </c>
       <c r="C31">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>315</v>
       </c>
       <c r="B32">
-        <v>7.725</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="C32">
         <v>16.2</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>316</v>
       </c>
       <c r="B33">
-        <v>7.975</v>
+        <v>7.9749999999999996</v>
       </c>
       <c r="C33">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>317</v>
       </c>
       <c r="B34">
-        <v>8.225</v>
+        <v>8.2249999999999996</v>
       </c>
       <c r="C34">
         <v>16.3</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>318</v>
       </c>
       <c r="B35">
-        <v>8.475</v>
+        <v>8.4749999999999996</v>
       </c>
       <c r="C35">
         <v>17.2</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>319</v>
       </c>
       <c r="B36">
-        <v>8.725</v>
+        <v>8.7249999999999996</v>
       </c>
       <c r="C36">
         <v>16.7</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>320</v>
       </c>
       <c r="B37">
-        <v>8.975</v>
+        <v>8.9749999999999996</v>
       </c>
       <c r="C37">
         <v>16.5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>321</v>
       </c>
       <c r="B38">
-        <v>9.225</v>
+        <v>9.2249999999999996</v>
       </c>
       <c r="C38">
         <v>16</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>321</v>
       </c>
       <c r="B39">
-        <v>9.225</v>
+        <v>9.2249999999999996</v>
       </c>
       <c r="C39">
         <v>16</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>322</v>
       </c>
       <c r="B40">
-        <v>9.475</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="C40">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>323</v>
       </c>
       <c r="B41">
-        <v>9.725</v>
+        <v>9.7249999999999996</v>
       </c>
       <c r="C41">
         <v>16.8</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>324</v>
       </c>
       <c r="B42">
-        <v>9.975</v>
+        <v>9.9749999999999996</v>
       </c>
       <c r="C42">
         <v>16.3</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>325</v>
       </c>
@@ -2825,10 +2849,10 @@
         <v>10.225</v>
       </c>
       <c r="C43">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>326</v>
       </c>
@@ -2836,10 +2860,10 @@
         <v>10.475</v>
       </c>
       <c r="C44">
-        <v>17.4</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>327</v>
       </c>
@@ -2850,7 +2874,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -2858,21 +2882,23 @@
         <v>10.975</v>
       </c>
       <c r="C46">
-        <v>16.4</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C46"/>
+    <ignoredError sqref="A1:C46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>282</v>
       </c>
@@ -2883,458 +2909,458 @@
         <v>168</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>285</v>
       </c>
       <c r="B2">
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="C2">
         <v>1085</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>286</v>
       </c>
       <c r="B3">
-        <v>0.475</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="C3">
         <v>1085</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>287</v>
       </c>
       <c r="B4">
-        <v>0.725</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="C4">
         <v>1085</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>288</v>
       </c>
       <c r="B5">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="C5">
         <v>1083</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>289</v>
       </c>
       <c r="B6">
-        <v>1.225</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="C6">
         <v>1082</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>290</v>
       </c>
       <c r="B7">
-        <v>1.475</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="C7">
         <v>1077</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>291</v>
       </c>
       <c r="B8">
-        <v>1.725</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="C8">
         <v>1074</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>292</v>
       </c>
       <c r="B9">
-        <v>1.975</v>
+        <v>1.9750000000000001</v>
       </c>
       <c r="C9">
         <v>1068</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>293</v>
       </c>
       <c r="B10">
-        <v>2.225</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="C10">
         <v>1062</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>294</v>
       </c>
       <c r="B11">
-        <v>2.475</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="C11">
         <v>1053</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>295</v>
       </c>
       <c r="B12">
-        <v>2.725</v>
+        <v>2.7250000000000001</v>
       </c>
       <c r="C12">
         <v>1048</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>296</v>
       </c>
       <c r="B13">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="C13">
         <v>1043</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>297</v>
       </c>
       <c r="B14">
-        <v>3.225</v>
+        <v>3.2250000000000001</v>
       </c>
       <c r="C14">
         <v>1041</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>298</v>
       </c>
       <c r="B15">
-        <v>3.475</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="C15">
         <v>1035</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>299</v>
       </c>
       <c r="B16">
-        <v>3.725</v>
+        <v>3.7250000000000001</v>
       </c>
       <c r="C16">
         <v>1030</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>300</v>
       </c>
       <c r="B17">
-        <v>3.975</v>
+        <v>3.9750000000000001</v>
       </c>
       <c r="C17">
         <v>1029</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>301</v>
       </c>
       <c r="B18">
-        <v>4.225</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="C18">
         <v>1026</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>302</v>
       </c>
       <c r="B19">
-        <v>4.475</v>
+        <v>4.4749999999999996</v>
       </c>
       <c r="C19">
         <v>1021</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>303</v>
       </c>
       <c r="B20">
-        <v>4.725</v>
+        <v>4.7249999999999996</v>
       </c>
       <c r="C20">
         <v>1018</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>304</v>
       </c>
       <c r="B21">
-        <v>4.975</v>
+        <v>4.9749999999999996</v>
       </c>
       <c r="C21">
         <v>1015</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>305</v>
       </c>
       <c r="B22">
-        <v>5.225</v>
+        <v>5.2249999999999996</v>
       </c>
       <c r="C22">
         <v>1015</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>306</v>
       </c>
       <c r="B23">
-        <v>5.475</v>
+        <v>5.4749999999999996</v>
       </c>
       <c r="C23">
         <v>1013</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>307</v>
       </c>
       <c r="B24">
-        <v>5.725</v>
+        <v>5.7249999999999996</v>
       </c>
       <c r="C24">
         <v>1010</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>308</v>
       </c>
       <c r="B25">
-        <v>5.975</v>
+        <v>5.9749999999999996</v>
       </c>
       <c r="C25">
         <v>1008</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>309</v>
       </c>
       <c r="B26">
-        <v>6.225</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="C26">
         <v>1008</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>310</v>
       </c>
       <c r="B27">
-        <v>6.475</v>
+        <v>6.4749999999999996</v>
       </c>
       <c r="C27">
         <v>1005</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>311</v>
       </c>
       <c r="B28">
-        <v>6.725</v>
+        <v>6.7249999999999996</v>
       </c>
       <c r="C28">
         <v>1004</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>312</v>
       </c>
       <c r="B29">
-        <v>6.975</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="C29">
         <v>1003</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>313</v>
       </c>
       <c r="B30">
-        <v>7.225</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="C30">
         <v>1003</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>314</v>
       </c>
       <c r="B31">
-        <v>7.475</v>
+        <v>7.4749999999999996</v>
       </c>
       <c r="C31">
         <v>1000</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>315</v>
       </c>
       <c r="B32">
-        <v>7.725</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="C32">
         <v>1000</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>316</v>
       </c>
       <c r="B33">
-        <v>7.975</v>
+        <v>7.9749999999999996</v>
       </c>
       <c r="C33">
         <v>999</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>317</v>
       </c>
       <c r="B34">
-        <v>8.225</v>
+        <v>8.2249999999999996</v>
       </c>
       <c r="C34">
         <v>999</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>318</v>
       </c>
       <c r="B35">
-        <v>8.475</v>
+        <v>8.4749999999999996</v>
       </c>
       <c r="C35">
         <v>997</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>319</v>
       </c>
       <c r="B36">
-        <v>8.725</v>
+        <v>8.7249999999999996</v>
       </c>
       <c r="C36">
         <v>997</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>320</v>
       </c>
       <c r="B37">
-        <v>8.975</v>
+        <v>8.9749999999999996</v>
       </c>
       <c r="C37">
         <v>996</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>321</v>
       </c>
       <c r="B38">
-        <v>9.225</v>
+        <v>9.2249999999999996</v>
       </c>
       <c r="C38">
         <v>995</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>321</v>
       </c>
       <c r="B39">
-        <v>9.225</v>
+        <v>9.2249999999999996</v>
       </c>
       <c r="C39">
         <v>995</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>322</v>
       </c>
       <c r="B40">
-        <v>9.475</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="C40">
         <v>995</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>323</v>
       </c>
       <c r="B41">
-        <v>9.725</v>
+        <v>9.7249999999999996</v>
       </c>
       <c r="C41">
         <v>995</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>324</v>
       </c>
       <c r="B42">
-        <v>9.975</v>
+        <v>9.9749999999999996</v>
       </c>
       <c r="C42">
         <v>995</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>325</v>
       </c>
@@ -3345,7 +3371,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>326</v>
       </c>
@@ -3356,7 +3382,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>327</v>
       </c>
@@ -3367,7 +3393,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -3379,17 +3405,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C46"/>
+    <ignoredError sqref="A1:C46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>282</v>
       </c>
@@ -3413,17 +3441,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CW2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:101" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3728,7 +3758,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:101" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -3853,7 +3883,7 @@
         <v>142</v>
       </c>
       <c r="AS2">
-        <v>16.4</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="AT2">
         <v>11.6</v>
@@ -3943,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="BW2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BX2">
         <v>0</v>
@@ -3985,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="CK2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CL2">
         <v>0</v>
@@ -4009,21 +4039,23 @@
         <v>0</v>
       </c>
       <c r="CS2">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CW2"/>
+    <ignoredError sqref="A1:CW2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4076,7 +4108,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4105,7 +4137,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9842</v>
       </c>
@@ -4140,7 +4172,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9842</v>
       </c>
@@ -4169,7 +4201,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9842</v>
       </c>
@@ -4183,7 +4215,7 @@
         <v>182</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>178</v>
@@ -4219,7 +4251,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9842</v>
       </c>
@@ -4233,7 +4265,7 @@
         <v>182</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>178</v>
@@ -4269,7 +4301,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9842</v>
       </c>
@@ -4304,7 +4336,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9842</v>
       </c>
@@ -4351,7 +4383,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9842</v>
       </c>
@@ -4380,7 +4412,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9842</v>
       </c>
@@ -4415,7 +4447,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9842</v>
       </c>
@@ -4450,7 +4482,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9842</v>
       </c>
@@ -4486,17 +4518,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4528,7 +4562,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4560,7 +4594,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9842</v>
       </c>
@@ -4592,7 +4626,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9842</v>
       </c>
@@ -4625,27 +4659,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4677,7 +4715,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4710,17 +4748,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4737,7 +4777,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4749,27 +4789,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4819,7 +4863,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4832,7 +4876,7 @@
       <c r="D2">
         <v>6817</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.77616898148</v>
       </c>
       <c r="F2" t="s">
@@ -4863,13 +4907,13 @@
         <v>240</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9842</v>
       </c>
@@ -4882,7 +4926,7 @@
       <c r="D3">
         <v>6817</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.77616898148</v>
       </c>
       <c r="F3" t="s">
@@ -4913,13 +4957,13 @@
         <v>240</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9842</v>
       </c>
@@ -4932,7 +4976,7 @@
       <c r="D4">
         <v>6817</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.77616898148</v>
       </c>
       <c r="F4" t="s">
@@ -4969,7 +5013,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9842</v>
       </c>
@@ -4982,7 +5026,7 @@
       <c r="D5">
         <v>6817</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.77616898148</v>
       </c>
       <c r="F5" t="s">
@@ -5019,7 +5063,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9842</v>
       </c>
@@ -5032,7 +5076,7 @@
       <c r="D6">
         <v>6817</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.77616898148</v>
       </c>
       <c r="F6" t="s">
@@ -5069,7 +5113,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9842</v>
       </c>
@@ -5082,7 +5126,7 @@
       <c r="D7">
         <v>6817</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.77616898148</v>
       </c>
       <c r="F7" t="s">
@@ -5119,7 +5163,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9842</v>
       </c>
@@ -5132,7 +5176,7 @@
       <c r="D8">
         <v>6817</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.77616898148</v>
       </c>
       <c r="F8" t="s">
@@ -5169,7 +5213,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9842</v>
       </c>
@@ -5182,8 +5226,8 @@
       <c r="D9">
         <v>6883</v>
       </c>
-      <c r="E9">
-        <v>45376.65739583333</v>
+      <c r="E9" s="1">
+        <v>45373.657395833332</v>
       </c>
       <c r="F9" t="s">
         <v>131</v>
@@ -5213,13 +5257,13 @@
         <v>240</v>
       </c>
       <c r="O9">
-        <v>7.8336</v>
+        <v>7.8335999999999997</v>
       </c>
       <c r="P9" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9842</v>
       </c>
@@ -5232,8 +5276,8 @@
       <c r="D10">
         <v>6883</v>
       </c>
-      <c r="E10">
-        <v>45376.65739583333</v>
+      <c r="E10" s="1">
+        <v>45373.657395833332</v>
       </c>
       <c r="F10" t="s">
         <v>131</v>
@@ -5269,7 +5313,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9842</v>
       </c>
@@ -5282,8 +5326,8 @@
       <c r="D11">
         <v>6883</v>
       </c>
-      <c r="E11">
-        <v>45376.65739583333</v>
+      <c r="E11" s="1">
+        <v>45373.657395833332</v>
       </c>
       <c r="F11" t="s">
         <v>131</v>
@@ -5313,13 +5357,13 @@
         <v>240</v>
       </c>
       <c r="O11">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="P11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9842</v>
       </c>
@@ -5332,8 +5376,8 @@
       <c r="D12">
         <v>6883</v>
       </c>
-      <c r="E12">
-        <v>45376.65739583333</v>
+      <c r="E12" s="1">
+        <v>45373.657395833332</v>
       </c>
       <c r="F12" t="s">
         <v>131</v>
@@ -5369,7 +5413,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9842</v>
       </c>
@@ -5382,8 +5426,8 @@
       <c r="D13">
         <v>6883</v>
       </c>
-      <c r="E13">
-        <v>45376.65739583333</v>
+      <c r="E13" s="1">
+        <v>45373.657395833332</v>
       </c>
       <c r="F13" t="s">
         <v>131</v>
@@ -5419,7 +5463,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9842</v>
       </c>
@@ -5432,8 +5476,8 @@
       <c r="D14">
         <v>6883</v>
       </c>
-      <c r="E14">
-        <v>45376.65739583333</v>
+      <c r="E14" s="1">
+        <v>45373.657395833332</v>
       </c>
       <c r="F14" t="s">
         <v>131</v>
@@ -5463,13 +5507,13 @@
         <v>240</v>
       </c>
       <c r="O14">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="P14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9842</v>
       </c>
@@ -5482,8 +5526,8 @@
       <c r="D15">
         <v>6883</v>
       </c>
-      <c r="E15">
-        <v>45376.65739583333</v>
+      <c r="E15" s="1">
+        <v>45373.657395833332</v>
       </c>
       <c r="F15" t="s">
         <v>131</v>
@@ -5519,7 +5563,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9842</v>
       </c>
@@ -5532,8 +5576,8 @@
       <c r="D16">
         <v>7100</v>
       </c>
-      <c r="E16">
-        <v>45383.62342592592</v>
+      <c r="E16" s="1">
+        <v>45383.623425925922</v>
       </c>
       <c r="F16" t="s">
         <v>131</v>
@@ -5569,7 +5613,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9842</v>
       </c>
@@ -5582,7 +5626,7 @@
       <c r="D17">
         <v>7165</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>45384.852268518516</v>
       </c>
       <c r="F17" t="s">
@@ -5619,7 +5663,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9842</v>
       </c>
@@ -5632,8 +5676,8 @@
       <c r="D18">
         <v>7248</v>
       </c>
-      <c r="E18">
-        <v>45386.86924768519</v>
+      <c r="E18" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F18" t="s">
         <v>131</v>
@@ -5669,7 +5713,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9842</v>
       </c>
@@ -5682,8 +5726,8 @@
       <c r="D19">
         <v>7248</v>
       </c>
-      <c r="E19">
-        <v>45386.86924768519</v>
+      <c r="E19" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F19" t="s">
         <v>131</v>
@@ -5713,13 +5757,13 @@
         <v>240</v>
       </c>
       <c r="O19">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P19" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9842</v>
       </c>
@@ -5732,8 +5776,8 @@
       <c r="D20">
         <v>7248</v>
       </c>
-      <c r="E20">
-        <v>45386.86924768519</v>
+      <c r="E20" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F20" t="s">
         <v>131</v>
@@ -5769,7 +5813,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9842</v>
       </c>
@@ -5782,8 +5826,8 @@
       <c r="D21">
         <v>7248</v>
       </c>
-      <c r="E21">
-        <v>45386.86924768519</v>
+      <c r="E21" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F21" t="s">
         <v>131</v>
@@ -5819,7 +5863,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9842</v>
       </c>
@@ -5832,8 +5876,8 @@
       <c r="D22">
         <v>7248</v>
       </c>
-      <c r="E22">
-        <v>45386.86924768519</v>
+      <c r="E22" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F22" t="s">
         <v>131</v>
@@ -5869,7 +5913,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9842</v>
       </c>
@@ -5882,8 +5926,8 @@
       <c r="D23">
         <v>7248</v>
       </c>
-      <c r="E23">
-        <v>45386.86924768519</v>
+      <c r="E23" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F23" t="s">
         <v>131</v>
@@ -5913,13 +5957,13 @@
         <v>240</v>
       </c>
       <c r="O23">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="P23" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9842</v>
       </c>
@@ -5932,8 +5976,8 @@
       <c r="D24">
         <v>7248</v>
       </c>
-      <c r="E24">
-        <v>45386.86924768519</v>
+      <c r="E24" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F24" t="s">
         <v>131</v>
@@ -5969,7 +6013,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9842</v>
       </c>
@@ -5982,8 +6026,8 @@
       <c r="D25">
         <v>7248</v>
       </c>
-      <c r="E25">
-        <v>45386.86924768519</v>
+      <c r="E25" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F25" t="s">
         <v>131</v>
@@ -6019,7 +6063,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9842</v>
       </c>
@@ -6032,8 +6076,8 @@
       <c r="D26">
         <v>7248</v>
       </c>
-      <c r="E26">
-        <v>45386.86924768519</v>
+      <c r="E26" s="1">
+        <v>45386.869247685187</v>
       </c>
       <c r="F26" t="s">
         <v>131</v>
@@ -6069,7 +6113,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9842</v>
       </c>
@@ -6082,7 +6126,7 @@
       <c r="D27">
         <v>7419</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F27" t="s">
@@ -6119,7 +6163,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9842</v>
       </c>
@@ -6132,7 +6176,7 @@
       <c r="D28">
         <v>7419</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F28" t="s">
@@ -6163,13 +6207,13 @@
         <v>240</v>
       </c>
       <c r="O28">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P28" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9842</v>
       </c>
@@ -6182,7 +6226,7 @@
       <c r="D29">
         <v>7419</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F29" t="s">
@@ -6219,7 +6263,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9842</v>
       </c>
@@ -6232,7 +6276,7 @@
       <c r="D30">
         <v>7419</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F30" t="s">
@@ -6269,7 +6313,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9842</v>
       </c>
@@ -6282,7 +6326,7 @@
       <c r="D31">
         <v>7419</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F31" t="s">
@@ -6313,13 +6357,13 @@
         <v>240</v>
       </c>
       <c r="O31">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="P31" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9842</v>
       </c>
@@ -6332,7 +6376,7 @@
       <c r="D32">
         <v>7419</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F32" t="s">
@@ -6369,7 +6413,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9842</v>
       </c>
@@ -6382,7 +6426,7 @@
       <c r="D33">
         <v>7419</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F33" t="s">
@@ -6413,13 +6457,13 @@
         <v>240</v>
       </c>
       <c r="O33">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="P33" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9842</v>
       </c>
@@ -6432,7 +6476,7 @@
       <c r="D34">
         <v>7419</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F34" t="s">
@@ -6469,7 +6513,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9842</v>
       </c>
@@ -6482,7 +6526,7 @@
       <c r="D35">
         <v>7419</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F35" t="s">
@@ -6519,7 +6563,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9842</v>
       </c>
@@ -6532,7 +6576,7 @@
       <c r="D36">
         <v>7419</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="1">
         <v>45391.68513888889</v>
       </c>
       <c r="F36" t="s">
@@ -6570,8 +6614,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P36"/>
+    <ignoredError sqref="A1:P8 A16:P36 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Datos Experimentales/Data 24022.xlsx
+++ b/Datos Experimentales/Data 24022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B979E88-ABC9-412B-B7A1-48509CD54DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF6A2B5-5FA2-457B-AF31-53AC6AFA57CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1407,9 +1407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>89</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>123</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>124</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2332,7 +2332,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2344,9 +2344,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -2377,9 +2377,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>282</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>285</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>286</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>287</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>288</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>289</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>290</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>291</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>292</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>293</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>294</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>295</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>296</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>297</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>298</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>299</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>300</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>301</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>302</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>303</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>304</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>305</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>306</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>307</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>308</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>309</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>310</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>311</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>312</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>313</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>314</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>315</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>316</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>317</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>318</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>319</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>320</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>321</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>321</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>322</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>323</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>324</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>325</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>326</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>327</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -2896,9 +2896,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>282</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>285</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>286</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>287</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>288</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>289</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>290</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>291</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>292</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>293</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>294</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>295</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>296</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>297</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>298</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>299</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>300</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>301</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>302</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>303</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>304</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>305</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>306</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>307</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>308</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>309</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>310</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>311</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>312</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>313</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>314</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>315</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>316</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>317</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>318</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>319</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>320</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>321</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>321</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>322</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>323</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>324</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>325</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>326</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>327</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -3415,9 +3415,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>282</v>
       </c>
@@ -3451,9 +3451,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CW2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:101" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:101" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4053,9 +4053,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9842</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9842</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9842</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9842</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9842</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9842</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9842</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9842</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9842</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9842</v>
       </c>
@@ -4528,9 +4528,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9842</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9842</v>
       </c>
@@ -4669,7 +4669,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4681,9 +4681,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4758,9 +4758,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4799,7 +4799,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4811,9 +4811,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>157</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9842</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9842</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9842</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9842</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9842</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9842</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9842</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9842</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>248</v>
       </c>
       <c r="J9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K9" t="s">
         <v>250</v>
@@ -5263,7 +5263,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9842</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>248</v>
       </c>
       <c r="J10" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K10" t="s">
         <v>241</v>
@@ -5313,7 +5313,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9842</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>248</v>
       </c>
       <c r="J11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K11" t="s">
         <v>242</v>
@@ -5363,7 +5363,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9842</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>248</v>
       </c>
       <c r="J12" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K12" t="s">
         <v>244</v>
@@ -5413,7 +5413,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9842</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>248</v>
       </c>
       <c r="J13" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K13" t="s">
         <v>251</v>
@@ -5463,7 +5463,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9842</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>248</v>
       </c>
       <c r="J14" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K14" t="s">
         <v>252</v>
@@ -5513,7 +5513,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9842</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>248</v>
       </c>
       <c r="J15" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K15" t="s">
         <v>247</v>
@@ -5563,7 +5563,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9842</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9842</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9842</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9842</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9842</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9842</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9842</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9842</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9842</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9842</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9842</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9842</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>248</v>
       </c>
       <c r="J27" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K27" t="s">
         <v>250</v>
@@ -6163,7 +6163,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9842</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>248</v>
       </c>
       <c r="J28" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K28" t="s">
         <v>257</v>
@@ -6213,7 +6213,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9842</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>248</v>
       </c>
       <c r="J29" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K29" t="s">
         <v>259</v>
@@ -6263,7 +6263,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9842</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>248</v>
       </c>
       <c r="J30" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K30" t="s">
         <v>254</v>
@@ -6313,7 +6313,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9842</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>248</v>
       </c>
       <c r="J31" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K31" t="s">
         <v>272</v>
@@ -6363,7 +6363,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9842</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>248</v>
       </c>
       <c r="J32" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K32" t="s">
         <v>262</v>
@@ -6413,7 +6413,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9842</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>248</v>
       </c>
       <c r="J33" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K33" t="s">
         <v>264</v>
@@ -6463,7 +6463,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9842</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>248</v>
       </c>
       <c r="J34" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K34" t="s">
         <v>244</v>
@@ -6513,7 +6513,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9842</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>248</v>
       </c>
       <c r="J35" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K35" t="s">
         <v>251</v>
@@ -6563,7 +6563,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9842</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>248</v>
       </c>
       <c r="J36" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K36" t="s">
         <v>252</v>
@@ -6616,7 +6616,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P8 A16:P36 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P8 A16:P26 A9:D9 F9:I9 A10:D15 F10:I15 A27:I36 K27:P36 K9:P9 K10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>